--- a/data/trans_dic/P22$concerIndv-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P22$concerIndv-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguro Médico concertado individualmente</t>
+          <t>Población que, al menos, es beneficiaria de seguro médico concertado individualmente (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,15; 8,71</t>
+          <t>3,03; 8,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,81; 10,34</t>
+          <t>3,97; 10,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,05; 8,08</t>
+          <t>3,11; 8,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,6; 11,91</t>
+          <t>3,47; 11,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 9,78</t>
+          <t>3,06; 9,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,97; 8,51</t>
+          <t>2,84; 8,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,97; 8,82</t>
+          <t>2,83; 8,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,8; 14,13</t>
+          <t>7,67; 14,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,81; 7,97</t>
+          <t>3,87; 8,02</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,0; 8,34</t>
+          <t>4,18; 8,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,5; 7,46</t>
+          <t>3,49; 7,24</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,18; 11,51</t>
+          <t>6,29; 11,37</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,5</t>
+          <t>0,82; 3,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 5,72</t>
+          <t>1,93; 5,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,74</t>
+          <t>0,41; 2,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,73</t>
+          <t>1,47; 4,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,9</t>
+          <t>1,54; 4,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,54; 6,41</t>
+          <t>2,79; 6,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,77</t>
+          <t>1,59; 4,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,08</t>
+          <t>2,14; 4,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,39</t>
+          <t>1,32; 3,38</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,32</t>
+          <t>2,76; 5,45</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,16</t>
+          <t>1,33; 3,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,17</t>
+          <t>2,09; 4,12</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,84</t>
+          <t>1,16; 4,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 4,59</t>
+          <t>0,6; 5,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,95</t>
+          <t>0,57; 3,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,68; 8,45</t>
+          <t>3,51; 8,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,9</t>
+          <t>0,3; 2,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,43</t>
+          <t>0,52; 4,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,43</t>
+          <t>0,57; 3,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 9,81</t>
+          <t>5,15; 9,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,08</t>
+          <t>1,0; 3,15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,54</t>
+          <t>0,84; 3,67</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,72</t>
+          <t>0,83; 2,61</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,96; 8,12</t>
+          <t>4,94; 8,11</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,92</t>
+          <t>0,83; 3,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,75; 8,85</t>
+          <t>4,0; 9,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,8; 13,2</t>
+          <t>5,9; 13,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,26</t>
+          <t>1,02; 4,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,23</t>
+          <t>1,73; 5,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,87; 9,22</t>
+          <t>3,82; 9,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,41; 8,24</t>
+          <t>3,34; 8,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,64</t>
+          <t>0,69; 2,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,01</t>
+          <t>1,6; 4,03</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,38; 8,09</t>
+          <t>4,44; 7,93</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,79; 9,63</t>
+          <t>4,78; 9,43</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,62</t>
+          <t>1,25; 5,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 8,1</t>
+          <t>1,81; 7,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,75; 8,08</t>
+          <t>2,83; 7,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,02; 9,6</t>
+          <t>2,66; 9,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,43; 10,21</t>
+          <t>3,43; 9,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,28</t>
+          <t>0,0; 2,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,12; 9,21</t>
+          <t>4,38; 9,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,71; 6,7</t>
+          <t>2,55; 6,47</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,32; 7,34</t>
+          <t>3,16; 7,46</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,87</t>
+          <t>0,2; 1,47</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,97; 7,63</t>
+          <t>4,07; 7,71</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,38</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 5,35</t>
+          <t>0,33; 4,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,36</t>
+          <t>0,35; 2,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,9; 7,28</t>
+          <t>2,7; 7,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,56</t>
+          <t>0,36; 3,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,67</t>
+          <t>0,35; 4,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,0</t>
+          <t>0,37; 3,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,96; 8,91</t>
+          <t>3,93; 9,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,17</t>
+          <t>0,38; 2,13</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,13</t>
+          <t>0,49; 3,15</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,29</t>
+          <t>0,38; 2,28</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,96; 7,31</t>
+          <t>4,06; 7,53</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,38</t>
+          <t>1,69; 4,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,1</t>
+          <t>1,38; 3,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,39; 7,2</t>
+          <t>3,54; 7,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,93; 16,92</t>
+          <t>10,83; 16,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,72</t>
+          <t>3,27; 7,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,92</t>
+          <t>1,37; 3,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,05; 7,6</t>
+          <t>4,09; 7,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,54; 18,35</t>
+          <t>6,21; 18,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,93; 5,19</t>
+          <t>2,85; 5,2</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,41</t>
+          <t>1,67; 3,58</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,17; 6,67</t>
+          <t>4,22; 6,67</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,43; 16,02</t>
+          <t>8,64; 16,31</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,03; 6,11</t>
+          <t>3,03; 6,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,04; 6,15</t>
+          <t>3,0; 5,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,34</t>
+          <t>2,43; 5,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,8</t>
+          <t>0,94; 3,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,34; 8,02</t>
+          <t>4,32; 7,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,94</t>
+          <t>2,25; 4,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,1; 8,63</t>
+          <t>5,06; 8,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,28; 7,46</t>
+          <t>4,36; 7,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,08; 6,34</t>
+          <t>4,11; 6,36</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,05; 5,01</t>
+          <t>3,04; 5,01</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,19; 6,51</t>
+          <t>4,14; 6,4</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,03</t>
+          <t>2,25; 5,05</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,31; 3,4</t>
+          <t>2,27; 3,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,66; 3,95</t>
+          <t>2,62; 3,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,75; 4,09</t>
+          <t>2,76; 4,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,66; 7,06</t>
+          <t>4,78; 7,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,28; 4,66</t>
+          <t>3,28; 4,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,05</t>
+          <t>2,71; 4,08</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,77; 5,25</t>
+          <t>3,74; 5,18</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,27; 8,7</t>
+          <t>6,25; 8,7</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,9; 3,82</t>
+          <t>2,97; 3,85</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,87; 3,74</t>
+          <t>2,87; 3,76</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,48; 4,45</t>
+          <t>3,47; 4,43</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,97; 7,6</t>
+          <t>5,93; 7,67</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguro Médico concertado individualmente</t>
+          <t>Población que, al menos, es beneficiaria de seguro médico concertado individualmente (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8568; 23708</t>
+          <t>8248; 24296</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11229; 30462</t>
+          <t>11688; 29498</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8972; 23723</t>
+          <t>9139; 24599</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11211; 37086</t>
+          <t>10820; 35695</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7727; 25498</t>
+          <t>7985; 24089</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8536; 24435</t>
+          <t>8159; 24557</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8532; 25368</t>
+          <t>8150; 24809</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22588; 40933</t>
+          <t>22218; 40855</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20285; 42472</t>
+          <t>20632; 42718</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23294; 48544</t>
+          <t>24330; 48445</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20341; 43396</t>
+          <t>20284; 42127</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37155; 69202</t>
+          <t>37806; 68321</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3210; 17279</t>
+          <t>4045; 17782</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9077; 28843</t>
+          <t>9725; 27620</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2064; 13764</t>
+          <t>2051; 14071</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7933; 24519</t>
+          <t>7642; 24493</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7749; 24716</t>
+          <t>7746; 22837</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13283; 33593</t>
+          <t>14597; 36490</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8982; 24945</t>
+          <t>8295; 24630</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10888; 26139</t>
+          <t>11040; 25521</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14118; 33815</t>
+          <t>13200; 33748</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28083; 54712</t>
+          <t>28342; 56062</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13035; 32433</t>
+          <t>13642; 33447</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21737; 43049</t>
+          <t>21574; 42617</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3744; 15444</t>
+          <t>3701; 15839</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1050; 14871</t>
+          <t>1951; 16315</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1756; 9332</t>
+          <t>1811; 9888</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11628; 26697</t>
+          <t>11101; 25672</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1012; 9720</t>
+          <t>1000; 9891</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1803; 15105</t>
+          <t>1784; 16053</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1903; 11528</t>
+          <t>1927; 12464</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18083; 34236</t>
+          <t>17970; 34458</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6592; 20121</t>
+          <t>6560; 20588</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5690; 23517</t>
+          <t>5615; 24388</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4805; 17773</t>
+          <t>5422; 17037</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32962; 54043</t>
+          <t>32891; 53963</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 7103</t>
+          <t>0; 7392</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3127; 14644</t>
+          <t>3099; 14318</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13883; 32726</t>
+          <t>14783; 33394</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18121; 41246</t>
+          <t>18433; 41704</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3972; 15795</t>
+          <t>3776; 14841</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6580; 20347</t>
+          <t>6725; 21668</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15006; 35702</t>
+          <t>14786; 36095</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16215; 39222</t>
+          <t>15896; 39857</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5622; 19184</t>
+          <t>5001; 17879</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12830; 30581</t>
+          <t>12221; 30737</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33187; 61245</t>
+          <t>33584; 60055</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>37723; 75892</t>
+          <t>37685; 74326</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2514; 11422</t>
+          <t>2545; 11951</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4025; 17218</t>
+          <t>3839; 16112</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5419</t>
+          <t>0; 5415</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4922; 14440</t>
+          <t>5062; 14228</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6263; 19945</t>
+          <t>5534; 19637</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7540; 22424</t>
+          <t>7527; 21881</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4994</t>
+          <t>0; 4605</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8591; 19224</t>
+          <t>9131; 19197</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11142; 27547</t>
+          <t>10459; 26585</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14348; 31743</t>
+          <t>13676; 32228</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>883; 8019</t>
+          <t>875; 6306</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15389; 29560</t>
+          <t>15779; 29878</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6455</t>
+          <t>0; 6401</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>902; 14652</t>
+          <t>905; 12452</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>930; 8854</t>
+          <t>920; 7783</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7815; 19629</t>
+          <t>7273; 19943</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1009; 9888</t>
+          <t>1013; 8930</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>987; 10268</t>
+          <t>978; 11368</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>996; 8188</t>
+          <t>1011; 9080</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10188; 22902</t>
+          <t>10100; 23142</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2051; 11923</t>
+          <t>2073; 11680</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2822; 17337</t>
+          <t>2714; 17428</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2062; 12290</t>
+          <t>2049; 12212</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>20844; 38481</t>
+          <t>21380; 39675</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>10393; 26920</t>
+          <t>10373; 27965</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8783; 27161</t>
+          <t>9177; 26262</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22185; 47039</t>
+          <t>23152; 46225</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>68249; 105625</t>
+          <t>67592; 105640</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>20420; 42779</t>
+          <t>20820; 44618</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9566; 27172</t>
+          <t>9505; 26427</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27798; 52178</t>
+          <t>28109; 52377</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>55566; 155784</t>
+          <t>52728; 155572</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>36633; 64882</t>
+          <t>35672; 65058</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21563; 46271</t>
+          <t>22617; 48591</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>55815; 89417</t>
+          <t>56568; 89400</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>124162; 236022</t>
+          <t>127360; 240329</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>22500; 45317</t>
+          <t>22470; 44692</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>23709; 47888</t>
+          <t>23401; 46024</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>17620; 41543</t>
+          <t>18885; 40458</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8133; 35311</t>
+          <t>8763; 35326</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>34030; 62877</t>
+          <t>33855; 59677</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>19058; 40669</t>
+          <t>18538; 40739</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>42129; 71311</t>
+          <t>41805; 70920</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>30597; 53387</t>
+          <t>31222; 52018</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>62227; 96732</t>
+          <t>62731; 97033</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>48931; 80266</t>
+          <t>48741; 80371</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>67235; 104542</t>
+          <t>66508; 102630</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>39451; 82737</t>
+          <t>37019; 83080</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>75537; 111272</t>
+          <t>74314; 112315</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>91137; 135348</t>
+          <t>89588; 135994</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>93270; 138724</t>
+          <t>93646; 136753</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>161243; 244335</t>
+          <t>165539; 245205</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>110874; 157521</t>
+          <t>110901; 158730</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>96570; 144198</t>
+          <t>96514; 145060</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>133323; 185772</t>
+          <t>132445; 183409</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>229379; 318533</t>
+          <t>228905; 318257</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>193013; 253601</t>
+          <t>197272; 256187</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>200265; 261234</t>
+          <t>200489; 262950</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>241127; 308326</t>
+          <t>240378; 306778</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>425087; 540954</t>
+          <t>422439; 546280</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$concerIndv-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P22$concerIndv-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,03; 8,93</t>
+          <t>3,32; 8,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,97; 10,01</t>
+          <t>4,01; 10,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,11; 8,37</t>
+          <t>2,93; 8,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 11,46</t>
+          <t>3,22; 9,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,06; 9,24</t>
+          <t>3,3; 9,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 8,55</t>
+          <t>2,93; 8,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 8,62</t>
+          <t>2,85; 8,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,67; 14,11</t>
+          <t>7,04; 12,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,87; 8,02</t>
+          <t>3,85; 7,95</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,18; 8,32</t>
+          <t>4,12; 8,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,49; 7,24</t>
+          <t>3,37; 7,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,29; 11,37</t>
+          <t>5,79; 9,82</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,61</t>
+          <t>0,66; 3,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,47</t>
+          <t>1,81; 5,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,8</t>
+          <t>0,41; 2,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,72</t>
+          <t>1,77; 5,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,53</t>
+          <t>1,49; 4,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,79; 6,97</t>
+          <t>2,61; 6,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,71</t>
+          <t>1,7; 4,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,96</t>
+          <t>2,02; 4,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,38</t>
+          <t>1,41; 3,53</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 5,45</t>
+          <t>2,75; 5,4</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,26</t>
+          <t>1,32; 3,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,12</t>
+          <t>2,32; 4,51</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,97</t>
+          <t>1,14; 5,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,03</t>
+          <t>0,6; 4,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,12</t>
+          <t>0,57; 3,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,51; 8,12</t>
+          <t>3,9; 8,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,95</t>
+          <t>0,3; 2,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,71</t>
+          <t>0,52; 4,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,71</t>
+          <t>0,58; 3,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,15; 9,87</t>
+          <t>5,17; 9,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,15</t>
+          <t>1,01; 3,19</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,67</t>
+          <t>0,85; 3,85</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,61</t>
+          <t>0,83; 2,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,94; 8,11</t>
+          <t>4,87; 8,23</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,83</t>
+          <t>0,84; 4,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,0; 9,03</t>
+          <t>3,68; 8,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,9; 13,34</t>
+          <t>5,94; 13,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,0</t>
+          <t>1,07; 4,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,57</t>
+          <t>1,72; 5,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,82; 9,32</t>
+          <t>3,64; 8,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,34; 8,38</t>
+          <t>5,69; 10,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,46</t>
+          <t>0,79; 2,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,03</t>
+          <t>1,62; 3,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,44; 7,93</t>
+          <t>4,21; 7,99</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,78; 9,43</t>
+          <t>6,24; 10,36</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,88</t>
+          <t>1,24; 5,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 7,58</t>
+          <t>2,22; 7,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,83; 7,96</t>
+          <t>2,46; 7,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,66; 9,46</t>
+          <t>2,9; 9,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,43; 9,96</t>
+          <t>3,41; 10,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,11</t>
+          <t>0,0; 2,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,38; 9,2</t>
+          <t>3,91; 8,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,55; 6,47</t>
+          <t>2,65; 6,78</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,16; 7,46</t>
+          <t>3,33; 7,54</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,47</t>
+          <t>0,2; 1,66</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,07; 7,71</t>
+          <t>3,69; 6,83</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,36</t>
+          <t>0,0; 2,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 4,54</t>
+          <t>0,35; 4,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,96</t>
+          <t>0,35; 3,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,7; 7,4</t>
+          <t>2,81; 7,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,21</t>
+          <t>0,36; 2,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,06</t>
+          <t>0,35; 3,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,32</t>
+          <t>0,37; 3,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,93; 9,0</t>
+          <t>3,97; 8,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,13</t>
+          <t>0,37; 2,15</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,49; 3,15</t>
+          <t>0,53; 3,34</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,28</t>
+          <t>0,39; 2,43</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,06; 7,53</t>
+          <t>3,7; 7,2</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,55</t>
+          <t>1,65; 4,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,96</t>
+          <t>1,25; 4,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,54; 7,07</t>
+          <t>3,43; 7,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,83; 16,92</t>
+          <t>11,42; 17,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,27; 7,0</t>
+          <t>3,3; 7,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,81</t>
+          <t>1,43; 3,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,09; 7,63</t>
+          <t>3,87; 7,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,21; 18,32</t>
+          <t>15,01; 19,86</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,2</t>
+          <t>2,89; 5,19</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,67; 3,58</t>
+          <t>1,63; 3,56</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,22; 6,67</t>
+          <t>4,23; 6,63</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,64; 16,31</t>
+          <t>13,89; 17,71</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,03; 6,03</t>
+          <t>2,97; 5,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,0; 5,91</t>
+          <t>3,04; 6,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,43; 5,2</t>
+          <t>2,38; 5,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,8</t>
+          <t>1,92; 4,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,32; 7,62</t>
+          <t>4,34; 7,76</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,94</t>
+          <t>2,35; 5,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,06; 8,58</t>
+          <t>5,29; 8,93</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,36; 7,27</t>
+          <t>4,08; 7,01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,11; 6,36</t>
+          <t>4,03; 6,29</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,04; 5,01</t>
+          <t>2,99; 4,98</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,14; 6,4</t>
+          <t>4,09; 6,47</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,05</t>
+          <t>3,45; 5,43</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -1837,42 +1837,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,43</t>
+          <t>2,29; 3,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,62; 3,97</t>
+          <t>2,64; 3,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,03</t>
+          <t>2,78; 3,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,78; 7,09</t>
+          <t>5,74; 7,57</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,28; 4,7</t>
+          <t>3,3; 4,62</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,08</t>
+          <t>2,76; 4,01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,74; 5,18</t>
+          <t>3,68; 5,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,25; 8,7</t>
+          <t>7,65; 9,25</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1882,17 +1882,17 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,87; 3,76</t>
+          <t>2,89; 3,81</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,47; 4,43</t>
+          <t>3,51; 4,45</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,93; 7,67</t>
+          <t>6,99; 8,1</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19720</t>
+          <t>17795</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30671</t>
+          <t>29939</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>50391</t>
+          <t>47734</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8248; 24296</t>
+          <t>9037; 23979</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11688; 29498</t>
+          <t>11819; 29915</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9139; 24599</t>
+          <t>8595; 24336</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10820; 35695</t>
+          <t>10260; 29883</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7985; 24089</t>
+          <t>8605; 24569</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8159; 24557</t>
+          <t>8421; 25304</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8150; 24809</t>
+          <t>8202; 25074</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22218; 40855</t>
+          <t>22250; 39607</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20632; 42718</t>
+          <t>20536; 42389</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24330; 48445</t>
+          <t>23960; 46598</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20284; 42127</t>
+          <t>19598; 43601</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37806; 68321</t>
+          <t>36753; 62317</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14532</t>
+          <t>16658</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16791</t>
+          <t>18042</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31324</t>
+          <t>34700</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4045; 17782</t>
+          <t>3251; 17837</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9725; 27620</t>
+          <t>9132; 28311</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2051; 14071</t>
+          <t>2078; 14524</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7642; 24493</t>
+          <t>9411; 27022</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7746; 22837</t>
+          <t>7512; 21902</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14597; 36490</t>
+          <t>13669; 34587</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8295; 24630</t>
+          <t>8896; 26048</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11040; 25521</t>
+          <t>11018; 25793</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13200; 33748</t>
+          <t>14071; 35178</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28342; 56062</t>
+          <t>28293; 55520</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13642; 33447</t>
+          <t>13530; 33646</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21574; 42617</t>
+          <t>25012; 48589</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17471</t>
+          <t>18465</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24848</t>
+          <t>24806</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>42319</t>
+          <t>43271</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3701; 15839</t>
+          <t>3635; 15945</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1951; 16315</t>
+          <t>1960; 14434</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1811; 9888</t>
+          <t>1807; 10110</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11101; 25672</t>
+          <t>12313; 27558</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1000; 9891</t>
+          <t>1007; 8953</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1784; 16053</t>
+          <t>1785; 15411</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1927; 12464</t>
+          <t>1957; 11724</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17970; 34458</t>
+          <t>18409; 33899</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6560; 20588</t>
+          <t>6607; 20864</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5615; 24388</t>
+          <t>5660; 25581</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5422; 17037</t>
+          <t>5417; 18578</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32891; 53963</t>
+          <t>32721; 55325</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27787</t>
+          <t>32793</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>28073</t>
+          <t>33250</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>55860</t>
+          <t>66043</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 7392</t>
+          <t>0; 7111</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3099; 14318</t>
+          <t>3160; 15010</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14783; 33394</t>
+          <t>13616; 32432</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18433; 41704</t>
+          <t>22151; 50347</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3776; 14841</t>
+          <t>3981; 15388</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6725; 21668</t>
+          <t>6675; 20462</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14786; 36095</t>
+          <t>14093; 34638</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15896; 39857</t>
+          <t>24024; 45101</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5001; 17879</t>
+          <t>5726; 18182</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12221; 30737</t>
+          <t>12354; 29413</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33584; 60055</t>
+          <t>31866; 60534</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>37685; 74326</t>
+          <t>49641; 82408</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>9159</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13425</t>
+          <t>12966</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21875</t>
+          <t>22125</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2545; 11951</t>
+          <t>2517; 11742</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3839; 16112</t>
+          <t>4725; 16407</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5415</t>
+          <t>0; 6256</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5062; 14228</t>
+          <t>5062; 15217</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5534; 19637</t>
+          <t>6030; 19069</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7527; 21881</t>
+          <t>7491; 22307</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4605</t>
+          <t>0; 4869</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9131; 19197</t>
+          <t>8878; 18421</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10459; 26585</t>
+          <t>10904; 27862</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13676; 32228</t>
+          <t>14399; 32584</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>875; 6306</t>
+          <t>876; 7141</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15779; 29878</t>
+          <t>15969; 29574</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13024</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>15598</t>
+          <t>16020</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>28623</t>
+          <t>28619</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6401</t>
+          <t>0; 7400</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>905; 12452</t>
+          <t>949; 11744</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>920; 7783</t>
+          <t>931; 8018</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7273; 19943</t>
+          <t>7614; 20238</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1013; 8930</t>
+          <t>1012; 8245</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>978; 11368</t>
+          <t>985; 10842</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1011; 9080</t>
+          <t>1006; 8308</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10100; 23142</t>
+          <t>10480; 23712</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2073; 11680</t>
+          <t>2037; 11801</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2714; 17428</t>
+          <t>2959; 18480</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2049; 12212</t>
+          <t>2080; 13049</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>21380; 39675</t>
+          <t>19790; 38501</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>84411</t>
+          <t>100318</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>111832</t>
+          <t>133816</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>196243</t>
+          <t>234134</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>10373; 27965</t>
+          <t>10142; 27446</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9177; 26262</t>
+          <t>8272; 26690</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23152; 46225</t>
+          <t>22400; 46326</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>67592; 105640</t>
+          <t>82164; 123336</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>20820; 44618</t>
+          <t>21039; 45437</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9505; 26427</t>
+          <t>9896; 27103</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28109; 52377</t>
+          <t>26587; 52069</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>52728; 155572</t>
+          <t>115725; 153125</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>35672; 65058</t>
+          <t>36136; 64911</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>22617; 48591</t>
+          <t>22058; 48319</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>56568; 89400</t>
+          <t>56723; 88806</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>127360; 240329</t>
+          <t>207001; 264063</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21963</t>
+          <t>24357</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>40957</t>
+          <t>45931</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>62920</t>
+          <t>70289</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>22470; 44692</t>
+          <t>22028; 44283</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>23401; 46024</t>
+          <t>23656; 48208</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>18885; 40458</t>
+          <t>18547; 41452</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8763; 35326</t>
+          <t>15343; 36403</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>33855; 59677</t>
+          <t>34014; 60774</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18538; 40739</t>
+          <t>19348; 42310</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>41805; 70920</t>
+          <t>43733; 73780</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>31222; 52018</t>
+          <t>33900; 58223</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>62731; 97033</t>
+          <t>61433; 95956</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>48741; 80371</t>
+          <t>47909; 79843</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>66508; 102630</t>
+          <t>65602; 103763</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>37019; 83080</t>
+          <t>56132; 88464</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>207358</t>
+          <t>232146</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>282196</t>
+          <t>314769</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>489554</t>
+          <t>546915</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>74314; 112315</t>
+          <t>74994; 111322</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>89588; 135994</t>
+          <t>90345; 134649</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>93646; 136753</t>
+          <t>94356; 135245</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>165539; 245205</t>
+          <t>202795; 267343</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>110901; 158730</t>
+          <t>111302; 156032</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>96514; 145060</t>
+          <t>98099; 142696</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>132445; 183409</t>
+          <t>130180; 182601</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>228905; 318257</t>
+          <t>285695; 345363</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>197272; 256187</t>
+          <t>197741; 255619</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>200489; 262950</t>
+          <t>202108; 266053</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>240378; 306778</t>
+          <t>243048; 308286</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>422439; 546280</t>
+          <t>507717; 588258</t>
         </is>
       </c>
     </row>
